--- a/test/excel/xlsx/roundtrip/struct-styles-styled.xlsx
+++ b/test/excel/xlsx/roundtrip/struct-styles-styled.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fxlsx-3324/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fxlsx-2614/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{05C7C5DC-7993-4548-A5C9-F55ACF1E2C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03B3EE59-734C-7F4A-B1BC-7291FA801A53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,13 +108,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -135,13 +135,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -528,10 +528,10 @@
       <c r="B3" s="1">
         <v>30</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="6">
         <v>3.5</v>
       </c>
     </row>
@@ -542,7 +542,7 @@
       <c r="B4" s="2">
         <v>40</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="7">
         <v>0.25</v>
       </c>
       <c r="D4" s="2"/>
@@ -554,19 +554,19 @@
       <c r="B5">
         <v>50</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" t="s">
+      <c r="D5" s="8"/>
+      <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="9">
         <v>1.25</v>
       </c>
     </row>
-    <row r="6" spans="1:10" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6">
+    <row r="6" spans="1:10" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
         <v>6</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <v>60</v>
       </c>
     </row>
@@ -586,11 +586,11 @@
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9">
+    <row r="9" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
         <v>9</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="4">
         <v>90</v>
       </c>
     </row>
